--- a/data/trans_dic/P36$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,29</t>
+          <t>0,56; 2,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,69</t>
+          <t>0,26; 1,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,57</t>
+          <t>4,83; 8,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,91</t>
+          <t>1,49; 3,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,17</t>
+          <t>0,5; 2,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,2</t>
+          <t>3,65; 7,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,65</t>
+          <t>1,25; 2,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,59</t>
+          <t>0,48; 1,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,29</t>
+          <t>4,61; 7,25</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,45</t>
+          <t>0,85; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,29; 1,41</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2,77; 5,41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,8; 2,23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,3; 1,4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,81; 5,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 2,23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 1,42</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,06</t>
+          <t>3,35; 6,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,09</t>
+          <t>0,95; 2,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,18</t>
+          <t>0,39; 1,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,41</t>
+          <t>3,49; 5,25</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,06</t>
+          <t>1,58; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,64</t>
+          <t>0,38; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,37</t>
+          <t>1,65; 4,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,05</t>
+          <t>1,0; 3,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,73</t>
+          <t>0,71; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,4</t>
+          <t>1,91; 4,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,16</t>
+          <t>1,51; 3,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,09</t>
+          <t>0,73; 2,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,86</t>
+          <t>2,1; 3,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,19</t>
+          <t>1,24; 3,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,89</t>
+          <t>0,97; 2,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,88</t>
+          <t>2,21; 4,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,04</t>
+          <t>0,68; 2,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,16</t>
+          <t>0,75; 2,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,23</t>
+          <t>2,83; 5,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,3</t>
+          <t>1,11; 2,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,13</t>
+          <t>1,01; 2,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,44</t>
+          <t>2,81; 4,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,33</t>
+          <t>1,42; 2,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,55</t>
+          <t>0,76; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,77</t>
+          <t>3,35; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,09</t>
+          <t>1,26; 2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,54</t>
+          <t>0,82; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,84</t>
+          <t>3,51; 4,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,08</t>
+          <t>1,41; 2,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,38</t>
+          <t>0,86; 1,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,61</t>
+          <t>3,62; 4,6</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4035; 15898</t>
+          <t>3867; 15624</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1839; 11868</t>
+          <t>1855; 11013</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31931; 57662</t>
+          <t>32478; 59161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10719; 26925</t>
+          <t>10287; 26228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3316; 15103</t>
+          <t>3475; 14927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24491; 48357</t>
+          <t>24504; 47803</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16514; 36585</t>
+          <t>17203; 36545</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6702; 22168</t>
+          <t>6725; 21327</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63074; 97979</t>
+          <t>62044; 97542</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7792; 23532</t>
+          <t>8121; 23682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3032; 14238</t>
+          <t>2977; 14369</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28728; 54975</t>
+          <t>28314; 55298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6927; 21562</t>
+          <t>7705; 21559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3120; 14669</t>
+          <t>3115; 14435</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33329; 63111</t>
+          <t>34928; 64902</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17704; 40168</t>
+          <t>18375; 39411</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8817; 24087</t>
+          <t>8034; 22868</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72253; 111585</t>
+          <t>71908; 108310</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10863; 27516</t>
+          <t>10701; 27015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2905; 19924</t>
+          <t>2877; 18890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13246; 33140</t>
+          <t>12505; 32594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7194; 20856</t>
+          <t>6825; 20742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5330; 21200</t>
+          <t>5493; 22095</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14996; 34504</t>
+          <t>15020; 34994</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21012; 43029</t>
+          <t>20553; 42912</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11360; 31984</t>
+          <t>11245; 32388</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32620; 59543</t>
+          <t>32471; 60646</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11553; 29990</t>
+          <t>11668; 30273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9124; 27382</t>
+          <t>9218; 26993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21428; 45796</t>
+          <t>20704; 42744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6695; 21075</t>
+          <t>7008; 21771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7829; 22717</t>
+          <t>7838; 23118</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29222; 54575</t>
+          <t>29527; 55194</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20540; 45426</t>
+          <t>21889; 44346</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19737; 42602</t>
+          <t>20234; 43013</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54827; 88015</t>
+          <t>55574; 89849</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46143; 76136</t>
+          <t>46331; 77733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24101; 52927</t>
+          <t>25950; 51016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114086; 161648</t>
+          <t>113648; 162985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41555; 70627</t>
+          <t>42427; 71113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29013; 54551</t>
+          <t>29090; 56910</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>125167; 171338</t>
+          <t>124407; 171662</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96628; 138150</t>
+          <t>93955; 138486</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61548; 96497</t>
+          <t>59747; 95957</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251277; 319791</t>
+          <t>251000; 318902</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,25</t>
+          <t>0,68; 2,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,25; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,79</t>
+          <t>4,88; 8,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,81</t>
+          <t>1,48; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,14</t>
+          <t>0,45; 2,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,12</t>
+          <t>3,6; 7,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,65</t>
+          <t>1,24; 2,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,53</t>
+          <t>0,43; 1,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,25</t>
+          <t>4,67; 7,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,47</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,41</t>
+          <t>0,3; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,41</t>
+          <t>2,93; 5,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,23</t>
+          <t>0,77; 2,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,4</t>
+          <t>0,31; 1,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,23</t>
+          <t>3,49; 6,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,05</t>
+          <t>0,93; 2,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,12</t>
+          <t>0,4; 1,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,25</t>
+          <t>3,53; 5,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,99</t>
+          <t>1,6; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,5</t>
+          <t>0,38; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,3</t>
+          <t>1,71; 4,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,03</t>
+          <t>1,05; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,85</t>
+          <t>0,68; 2,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,46</t>
+          <t>1,87; 4,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,15</t>
+          <t>1,53; 3,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,11</t>
+          <t>0,7; 2,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,93</t>
+          <t>2,15; 3,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,22</t>
+          <t>1,17; 3,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,85</t>
+          <t>0,96; 2,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,56</t>
+          <t>2,24; 4,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,1</t>
+          <t>0,62; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,2</t>
+          <t>0,74; 2,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,29</t>
+          <t>2,74; 5,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,24</t>
+          <t>1,09; 2,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,16</t>
+          <t>1,01; 2,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,54</t>
+          <t>2,82; 4,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,38</t>
+          <t>1,36; 2,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,49</t>
+          <t>0,74; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,81</t>
+          <t>3,38; 4,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,11</t>
+          <t>1,26; 2,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,6</t>
+          <t>0,82; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,85</t>
+          <t>3,56; 4,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,08</t>
+          <t>1,4; 2,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,38</t>
+          <t>0,88; 1,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,6</t>
+          <t>3,59; 4,62</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3867; 15624</t>
+          <t>4691; 15402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1855; 11013</t>
+          <t>1738; 10030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32478; 59161</t>
+          <t>32818; 57106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10287; 26228</t>
+          <t>10220; 26274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3475; 14927</t>
+          <t>3109; 14114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24504; 47803</t>
+          <t>24208; 47219</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17203; 36545</t>
+          <t>17103; 36785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6725; 21327</t>
+          <t>6042; 19883</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62044; 97542</t>
+          <t>62803; 97092</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8121; 23682</t>
+          <t>7758; 23146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2977; 14369</t>
+          <t>3013; 13431</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28314; 55298</t>
+          <t>29972; 55093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7705; 21559</t>
+          <t>7416; 21353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3115; 14435</t>
+          <t>3152; 14933</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34928; 64902</t>
+          <t>36398; 64630</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18375; 39411</t>
+          <t>17969; 39690</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8034; 22868</t>
+          <t>8164; 23611</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71908; 108310</t>
+          <t>72767; 112605</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10701; 27015</t>
+          <t>10864; 28259</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2877; 18890</t>
+          <t>2905; 18359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12505; 32594</t>
+          <t>12965; 32713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6825; 20742</t>
+          <t>7176; 20470</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5493; 22095</t>
+          <t>5315; 21792</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15020; 34994</t>
+          <t>14687; 35122</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20553; 42912</t>
+          <t>20844; 41322</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11245; 32388</t>
+          <t>10647; 33298</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32471; 60646</t>
+          <t>33212; 60709</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11668; 30273</t>
+          <t>10986; 30694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9218; 26993</t>
+          <t>9054; 26518</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20704; 42744</t>
+          <t>20979; 43266</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7008; 21771</t>
+          <t>6372; 20683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7838; 23118</t>
+          <t>7743; 22506</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29527; 55194</t>
+          <t>28530; 53464</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21889; 44346</t>
+          <t>21553; 44806</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20234; 43013</t>
+          <t>20081; 43326</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55574; 89849</t>
+          <t>55913; 90312</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46331; 77733</t>
+          <t>44323; 76151</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25950; 51016</t>
+          <t>25315; 50568</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113648; 162985</t>
+          <t>114546; 164189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42427; 71113</t>
+          <t>42586; 71838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29090; 56910</t>
+          <t>29161; 54949</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>124407; 171662</t>
+          <t>126126; 175735</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93955; 138486</t>
+          <t>93219; 136291</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59747; 95957</t>
+          <t>61139; 95274</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251000; 318902</t>
+          <t>248685; 320337</t>
         </is>
       </c>
     </row>
